--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -1035,7 +1035,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3654,23 +3654,19 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>26500000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>19386</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -4219,7 +4215,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4355,7 +4351,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4421,7 +4417,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4487,7 +4483,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4553,7 +4549,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4619,7 +4615,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4685,7 +4681,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -9000,7 +8996,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9010,7 +9006,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9092,7 @@
           <t>2 | 1367呎 (3房)
 $3120万
 $22,824/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9161,7 @@
           <t>2 | 1367呎 (3房)
 $3210万
 $23,482/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9276,7 @@
           <t>2 | 1367呎 (3房)
 $3481万
 $25,461/呎
-(23年-10月-29日)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9299,7 @@
           <t>2 | 1367呎 (3房)
 $3050万
 $22,312/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9322,7 @@
           <t>2 | 1367呎 (3房)
 $3363万
 $24,600/呎
-(23年-11月-16日)</t>
+(23年-11月-17日)</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9368,7 @@
           <t>2 | 1367呎 (3房)
 $3000万
 $21,946/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9383,7 @@
           <t>1 | 1363呎 (3房)
 $2780万
 $20,396/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9441,7 +9437,7 @@
           <t>2 | 1367呎 (2房)
 $2550万
 $18,654/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9506,7 @@
           <t>2 | 1367呎 (2房)
 $2750万
 $20,117/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -9528,12 +9524,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
--
--
-(待售)</t>
+$2650万
+$19,386/呎
+(26年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9621,7 @@
           <t>2 | 1367呎 (2房)
 $2500万
 $18,288/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9636,7 @@
           <t>1 | 1363呎 (2房)
 $2426万
 $17,800/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -9648,7 +9644,7 @@
           <t>2 | 1367呎 (2房)
 $2360万
 $17,264/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9659,7 @@
           <t>1 | 1363呎 (2房)
 $2605万
 $19,112/呎
-(23年-10月-26日)</t>
+(23年-10月-27日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -9671,7 +9667,7 @@
           <t>2 | 1367呎 (2房)
 $2310万
 $16,901/呎
-(24年-08月-08日)</t>
+(24年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9682,7 @@
           <t>1 | 1363呎 (2房)
 $2481万
 $18,200/呎
-(23年-10月-18日)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -9694,7 +9690,7 @@
           <t>2 | 1367呎 (2房)
 $2206万
 $16,134/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -2283,14 +2283,14 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>30500000</v>
+        <v>26500000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>22312</v>
+        <v>19386</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -9297,9 +9297,9 @@
       <c r="C16" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
-$3050万
-$22,312/呎
-(26年-06月-12日)</t>
+$2650万
+$19,386/呎
+(26年-08月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -2283,14 +2283,14 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>26500000</v>
+        <v>30500000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>19386</v>
+        <v>22312</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -9297,9 +9297,9 @@
       <c r="C16" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
-$2650万
-$19,386/呎
-(26年-08月-14日)</t>
+$3050万
+$22,312/呎
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
